--- a/output/Vendor_Manager_Jobs_2026-03-17.xlsx
+++ b/output/Vendor_Manager_Jobs_2026-03-17.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sourcing-procurement-manager-remote-at-lorven-technologies-inc-4385264881?position=1&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=FSuG8gn6agOJAP%2B4m0vDkw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/sourcing-procurement-manager-remote-at-lorven-technologies-inc-4385264881?position=1&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=hyB68kQnJvliljxGr%2BEGgw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/manager-supply-chain-fully-remote-at-lensa-4386345690?position=2&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=KYxxXVqnYwsQVOCtwIn4cg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/manager-supply-chain-fully-remote-at-lensa-4386345690?position=2&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=UfexDoNl5phsldCJ7tUADA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/professional-services-procurement-manager-at-the-fountain-group-4386529773?position=3&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=pJv65F2Gom%2B9vr1jSwBDXw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/professional-services-procurement-manager-at-the-fountain-group-4386529773?position=3&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=RcS4kKaZuqe8%2FBe5ZguXCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-manager-supply-chain-at-aurion-biotech-4386510897?position=4&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=hk0wQ5jSwlVYhxX0U2DqxA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-supply-chain-at-aurion-biotech-4386510897?position=4&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=X%2FC7d7Q9hlGFovuPjgp1UQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/director-of-vendor-management-at-reserv-4385272259?position=5&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=I9zzLg6r9gfcrTTYt83QrQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/director-of-vendor-management-at-reserv-4385272259?position=5&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=RK3kd8S9Ym4Yg4%2FhyF1uOQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/manager-procurement-operations-at-circular-action-alliance-4384096639?position=6&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=2oBcrGRckO7QXqGm5ouDVg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/manager-procurement-operations-at-circular-action-alliance-4384096639?position=6&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=nwOhoMvYA4etJXbm21A0qA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-business-development-leader-at-procureability-4385293919?position=7&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=lFRKzQG4eyx0ja7X6k88hg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-business-development-leader-at-procureability-4385293919?position=7&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=GqomWVLFCjsLI3oPxLNktQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-manager-protein-remote-at-lensa-4386361121?position=8&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=y%2BSfk3T50Ksm5t%2FH79fizw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-manager-protein-remote-at-lensa-4386361121?position=8&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=82SJUjLFYHMgWkTZWuf19A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-director-of-operations-at-lensa-4386349423?position=9&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=Dujfb2eHZ168VCCyHStdJQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-director-of-operations-at-lensa-4386349423?position=9&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=syZ2UaQrtwjde5e1c4u%2FGg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/idc-network-procurement-manager-north-america-remote-at-lingo-nova-4385259144?position=10&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=RjLjSbPMqutINzZMaxln4A%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/idc-network-procurement-manager-north-america-remote-at-lingo-nova-4385259144?position=10&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=etmQncoCNMS9%2BVF9nRIU3Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/supply-chain-program-manager-remote-at-lensa-4386339893?position=11&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=qA3dtgFyjqVK2IT2JWW7oA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/supply-chain-program-manager-remote-at-lensa-4386339893?position=11&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=ilUT1OwNT2f4C%2BChHSF8yA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/operations-manager-at-bravo-cpg-4385600485?position=12&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=V71sDDvlTn1cL32364pbkQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-at-bravo-cpg-4385600485?position=12&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=H6GAGPV0%2B1DmS5bKHO2o6Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/commodity-manager-service-supply-chain-management-at-otis-elevator-co-4382849382?position=13&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=TZumGDHDe5V3eRMjqVzbXw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/commodity-manager-service-supply-chain-management-at-otis-elevator-co-4382849382?position=13&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=B75tktZsxzyyg4OCw0v3eA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/ofci-equipment-procurement-manager-data-centers-at-nebius-4385610411?position=14&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=YW8CtUbjpc27gmFYcKv8wQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/ofci-equipment-procurement-manager-data-centers-at-nebius-4385610411?position=14&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=VHgXG8WT%2BoixPjLhMnBJdQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/enterprise-contracts-manager-remote-at-lensa-4386350547?position=15&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=%2Bn2K6f9cN4qwk5DF2B1TrA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/enterprise-contracts-manager-remote-at-lensa-4386350547?position=15&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=Q3aDEvDwf8g9ym2Y2c0kjQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/human-resources-generalist-at-peopleops-jobs-4386562312?position=16&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=xf4GRF6vWzaiabivKV1T3Q%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/human-resources-generalist-at-peopleops-jobs-4386562312?position=16&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=%2BTalYQScrP8%2B08sYQxzLgQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-manager-strategic-operations-at-coinbase-4386094615?position=17&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=6J4jrr3gRTtxFxtx3oCwbQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-strategic-operations-at-coinbase-4386094615?position=17&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=J0iOdl2kO0h2z1nA0wQE4w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-engineering-manager-supply-chain-at-ladders-4384058624?position=18&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=OExh4vPG2357ACzRs2Brag%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-engineering-manager-supply-chain-at-ladders-4384058624?position=18&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=19jSBKwZWCVF99chEkSlTQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/business-operations-manager-at-apex-systems-4386383220?position=19&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=PmzGhnjxtQ%2Bmb9CO6k9fVg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/business-operations-manager-at-apex-systems-4386383220?position=19&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=Chxdh8kys%2Bfo0hRWQ6XRKw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-sales-development-manager-logistics-transportation-remote-at-thermo-fisher-scientific-4386091526?position=20&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=hpPs%2BGANsKXyrWU8J829qw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-sales-development-manager-logistics-transportation-remote-at-thermo-fisher-scientific-4386091526?position=20&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=d5TWbLBAZ1eTSbMt3NIyLw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-manager-commercial-private-label-at-iff-4386518687?position=21&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=hkBGQtEW0xuJnqHCfdZyig%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-manager-commercial-private-label-at-iff-4386518687?position=21&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=IjoDoKuNyB6Yh3tuUl5XCw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/commercial-insurance-account-manager-transportation-at-capstone-search-group-4386536960?position=22&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=N01eyjwgp8vHhKWkL53h%2BA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/commercial-insurance-account-manager-transportation-at-capstone-search-group-4386536960?position=22&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=fX35Tgvd2l%2FSDbRDFfWeAw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-project-manager-vcf-at-the-redesign-group-4386362675?position=23&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=vUKsiB6tcW1ubbIjDiFNrw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-project-manager-vcf-at-the-redesign-group-4386362675?position=23&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=89NFepnI7MRNzSnN65BaBg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-specialist-4-remote-at-lensa-4386350430?position=24&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=8Y8HYhsChQbzoeGHHA%2F0VQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-specialist-4-remote-at-lensa-4386350430?position=24&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=SlRDGn2S42Zi51Ch%2FUtikA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/procurement-data-specialist-at-sodexo-4386516058?position=25&amp;pageNum=0&amp;refId=YT3TbmULK6o0j%2FN2p9NZHA%3D%3D&amp;trackingId=JZZtWxTWVo%2BPh44VqMS6Mw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/procurement-data-specialist-at-sodexo-4386516058?position=25&amp;pageNum=0&amp;refId=s9Wq%2FrtQrBZDmi%2FP6k7kOw%3D%3D&amp;trackingId=kvIg8PH4nT5vJH%2BoAFqeGA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/operations-manager-at-cookwise-ai-4384299869?position=1&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=a%2FEL%2BbBVL%2Bq4mVmFa0KKsw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-at-cookwise-ai-4384299869?position=1&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=xl3gPoNFAJ7aNJBFmGEKrg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/data-operations-manager-%2445-hr-remote-at-crossing-hurdles-4367558543?position=2&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=WTHe%2F%2Bhz4WWoAGMwlYcIUg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/data-operations-manager-%2445-hr-remote-at-crossing-hurdles-4367558543?position=2&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=S%2Blic5EoL4KGRohQHsqOMA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/strategy-operations-senior-manager-logistics-at-whatnot-4385283929?position=5&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=HFJTML6mKSE%2F6j4LY0rsBg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/strategy-operations-senior-manager-logistics-at-whatnot-4385283929?position=5&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=gnuLOkVU4aQXIp8vi23LcQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/retail-operations-manager-remote-at-mercor-4386381161?position=9&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=c%2BZuehnb%2FECPLkKc0LrHyQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/retail-operations-manager-remote-at-mercor-4386381161?position=9&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=S7ezvmMP75bj6SmgXFHBFg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/manager-business-operations-at-swooped-4386384337?position=11&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=bOORnIweYDfYhD7m71iX%2Fg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/manager-business-operations-at-swooped-4386384337?position=11&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=ArdI%2Boj0wDc39f49tNKrcQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/hospital-lab-operations-manager-at-lensa-4386359159?position=12&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=Hl0fU58r8Ib6Ch%2F%2BlLYJuw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/hospital-lab-operations-manager-at-lensa-4386359159?position=12&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=0vQlIfAbJ9mCe5ijgfNFpQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/business-operations-manager-at-swooped-4386382415?position=14&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=cX8WkfM4eeDvVsCpf21%2BdA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/business-operations-manager-at-swooped-4386382415?position=14&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=tuArcwQXGqwgKHv2pvzzWw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/operations-manager-remote-at-inspira-financial-4376808893?position=15&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=rK6FFg%2B7pztgr0ocbwL4TQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-remote-at-inspira-financial-4376808893?position=15&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=DSVGdoOJlWyzii9xyqKpxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/general-manager-north-america-at-bitvavo-app-4386556329?position=16&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=K%2B9iRmS6%2F5nYxwwaN5vXSQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/general-manager-north-america-at-bitvavo-app-4386556329?position=16&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=TVSDLyMYrOPw02mPvCMowg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/general-manager-integrator-operations-leader-%E2%80%93-remote-at-talent-harbor-4386369675?position=18&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=1ofsVYBNrGMOVvMwymagpw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/general-manager-integrator-operations-leader-%E2%80%93-remote-at-talent-harbor-4386369675?position=18&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=KAEjPiQ%2BBU89BI9q1otQ8Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/assembly-test-and-launch-operations-manager-at-space-ocean-corp-4386524960?position=19&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=cwNTB9x7f2DqSqJvVhuOZw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/assembly-test-and-launch-operations-manager-at-space-ocean-corp-4386524960?position=19&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=OP4%2F7opVeD69r6of%2ByUReQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/deputy-operations-manager-remote-at-network-runners-inc-4386381718?position=20&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=A%2FbJIuUFeHGGPsF9Gix5Bg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/deputy-operations-manager-remote-at-network-runners-inc-4386381718?position=20&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=4DvnVQDKaF5vWdxRh1sVOg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2312,17 +2312,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>Manager, Operations - Medical Record Retrieval (Remote)</t>
+          <t>Operations Manager (Remote)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>Lensa</t>
+          <t>Network Runners, Inc.</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>Sacramento, CA</t>
+          <t>Millington, TN</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/manager-operations-medical-record-retrieval-remote-at-lensa-4386360074?position=21&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=148W0yv%2FwLUp2wX%2BxEQipA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/operations-manager-remote-at-network-runners-inc-4386377819?position=21&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=MiaQ8Z3gbFdvD8GFGWjb1A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Operations Manager (Remote)</t>
+          <t>Manager, Operations - Medical Record Retrieval (Remote)</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Network Runners, Inc.</t>
+          <t>Lensa</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Millington, TN</t>
+          <t>Sacramento, CA</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr"/>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/operations-manager-remote-at-network-runners-inc-4386377819?position=22&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=u2Cz7EYnouEQPcDah6yBHQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/manager-operations-medical-record-retrieval-remote-at-lensa-4386360074?position=22&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=k6kspS9hy29GOIZFWc%2FlZw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/region-manager-north-atlantic-region-remote-at-lensa-4386339965?position=23&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=gqNFklRr%2FEB8gOz1HTancg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/region-manager-north-atlantic-region-remote-at-lensa-4386339965?position=23&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=VTTrRMyYEjo%2BVBzybCLWbA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/business-operations-manager-us-remote-at-remotehunter-4385608192?position=24&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=h7utWnfaw61NJ7ItcejCVQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/business-operations-manager-us-remote-at-remotehunter-4385608192?position=24&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=ohTKMbvsl%2FDfbbpBAhkO2g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/head-of-operations-shared-services-us-at-extenteam-4385282411?position=25&amp;pageNum=0&amp;refId=IdL%2BOZCiiYwVTysf5qvegw%3D%3D&amp;trackingId=LKbK8f8L3187bUoOBVcLRw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/head-of-operations-shared-services-us-at-extenteam-4385282411?position=25&amp;pageNum=0&amp;refId=ZgsWNpEIudpVCccR0X9XYQ%3D%3D&amp;trackingId=MdtddFuaRv0Dro1j8tfiYA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/contract-administrator-i-at-luna-data-solutions-inc-4385250993?position=4&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=ghRnh2yjad2lMQT%2FO2UDNw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/contract-administrator-i-at-luna-data-solutions-inc-4385250993?position=4&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=CzAEwNhlGEyTOaCzmbVlAw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/remote-administrative-assistant-1-at-lensa-4386356405?position=5&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=LToqkTb3%2FDIv%2Bq3Tz5sW6Q%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/remote-administrative-assistant-1-at-lensa-4386356405?position=5&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=E4WyfMQb5PN6Jmz%2Btcsb8Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/scheduling-coordinator-at-lensa-4386358244?position=6&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=1%2BeZGJD8YVywWYsF%2BFfbZg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/scheduling-coordinator-at-lensa-4386358244?position=6&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=CL2aIfGt2XLZFNtoxpYcRQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/project-support-coordinator-at-chevron-federal-credit-union-4386526779?position=7&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=gTlZRPIchMlQhGmQ%2By9L%2FQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/project-support-coordinator-at-chevron-federal-credit-union-4386526779?position=7&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=dxl6px3LvuGCDYvMAmb1RQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/administrative-assistant-idre-remote-at-improve-health-4385276223?position=8&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=MqOQp37i1EGmuQo%2BOUKrvw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-idre-remote-at-improve-health-4385276223?position=8&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=9BtI0Re1%2F6Cara2fBNCReA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/remote-associate-at-lensa-4386362008?position=9&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=XnVo0NFz8Pmi%2BiBad7vVmg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/remote-associate-at-lensa-4386362008?position=9&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=J7g9H9dd5LdML%2BU9P9AM5A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/principal-contract-administrator-remote-at-lensa-4386347648?position=10&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=OnHdMD3zDsYt0NA7B8tesA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/principal-contract-administrator-remote-at-lensa-4386347648?position=10&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=zCSuRu1FVd9GcKeaL483yw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/virtual-assistant-at-lensa-4386343604?position=11&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=wX3OCXAOmv9onumJIoEzVA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/virtual-assistant-at-lensa-4386343604?position=11&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=UnnZlpoRrjnX53ZNF7fllg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/project-assistant-at-hr-talent-board-4384080467?position=12&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=JiRlKQjAnfWsMNrIn2kQBA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/project-assistant-at-hr-talent-board-4384080467?position=12&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=Jeev12zpVNMqU7eB9coW8Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/enrollment-coordinator-at-insight-global-4385258857?position=13&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=4JcTiRmbOVGIxCgkIs839Q%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/enrollment-coordinator-at-insight-global-4385258857?position=13&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=8QXen%2FAzZbjEou4vThmjVg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/administrative-coordinator-first-aid-remote-at-lensa-4386356318?position=14&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=ZRNM4AiiWA7OEdsQzF4x8Q%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/administrative-coordinator-first-aid-remote-at-lensa-4386356318?position=14&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=bm5KNOkANGqnjKIGxUllyg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/administrative-assistant-i-at-wiraa-4385207406?position=16&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=N8QlTvrkddnVrzEDpqE1YA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-i-at-wiraa-4385207406?position=16&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=oy3Tw1d7o9NtB6xObGrixw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/processor-coordination-of-benefits-7-00-am-3-30-pm-pst-remote-at-lensa-4386348621?position=17&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=iJQtqq1LEZO2%2FhB7bpuq%2Bg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/processor-coordination-of-benefits-7-00-am-3-30-pm-pst-remote-at-lensa-4386348621?position=17&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=u0u09oz2McyjbPbv2%2B2m9A%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/administrative-assistant-at-wiraa-4385211263?position=18&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=3BiSoCnAcdA%2BUYCdhTZeyA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-at-wiraa-4385211263?position=18&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=G%2BWlNvAGiyM9t1RcMDeEdg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sr-contract-analyst-remote-at-lensa-4386358237?position=19&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=fK1uUp4byUidL1Cy60YjGg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/sr-contract-analyst-remote-at-lensa-4386358237?position=19&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=p9SWtk4Y5UKuyvLj1U4hpg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/remote-contract-specialist-iii-at-lensa-4386351509?position=21&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=SzoO%2BhNwLInXUq8hnMKJVw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/remote-contract-specialist-iii-at-lensa-4386351509?position=21&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=nENQt9%2Bqpi65zgY4JpWNug%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/remote-contract-specialist-ii-at-lensa-4386341852?position=27&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=1KlHZFbvyCnuCOxS66oyIQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/remote-contract-specialist-ii-at-lensa-4386341852?position=27&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=QGAiJq%2FJXZnRnyGsz7bWrg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/operations-dispatch-coordinator-remote-at-lensa-4386354345?position=28&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=FSGY9lC9S%2BIAglXd6Zm%2FkQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/operations-dispatch-coordinator-remote-at-lensa-4386354345?position=28&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=f2sv4ANRi8z4gxP6wU4nDg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/contract-manager-at-lhh-4385290425?position=29&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=CC5ZZZj5HN%2FbHF3F0SdT3Q%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/contract-manager-at-lhh-4385290425?position=29&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=0XW99Qj1awkXKI6mKEFVwQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/corporate-governance-administrator-remote-at-lensa-4386351383?position=30&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=BnF7m7mZvmCARiSzjA%2BD7A%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/corporate-governance-administrator-remote-at-lensa-4386351383?position=30&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=ClKQkDomaTdZJK0T6LU%2B%2Fw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/administrative-assistant-iv-at-swooped-4386374297?position=31&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=i4oJ03f7mWkzTk1UvbhZPQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/administrative-assistant-iv-at-swooped-4386374297?position=31&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=P2GtU%2Bq6sqSxxNB6djMZYQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/executive-admin-chief-of-staff-at-spire-international-group-llc-4385611975?position=32&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=xJJLanJsDq87SMJPz4mK4w%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/executive-admin-chief-of-staff-at-spire-international-group-llc-4385611975?position=32&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=iX72lWKaa%2BBDCqUQFbCt9g%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="J66" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/military-personnel-administrative-clerk-remote-at-wink-engineering-llc-4386524842?position=33&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=3p50P%2FUp%2Fov1sUum6P930w%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/military-personnel-administrative-clerk-remote-at-wink-engineering-llc-4386524842?position=33&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=PJSgT%2BsIzA8Wf8faK%2F0TJQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/workday-hcm-analyst-%E2%80%93-contract-at-american-arbitration-association-4384090625?position=34&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=vyRRfILnUofepa8%2BwD6uPA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/workday-hcm-analyst-%E2%80%93-contract-at-american-arbitration-association-4384090625?position=34&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=FTo%2BGEScwoi5AkvsBBYBjg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="J68" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/government-contracts-manager-at-lensa-4386350478?position=35&amp;pageNum=0&amp;refId=nJB4n4iOsqcm3DHgpbnF7w%3D%3D&amp;trackingId=kbBnG%2BH9gYjeB%2BOO5HQidg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/government-contracts-manager-at-lensa-4386350478?position=35&amp;pageNum=0&amp;refId=KoDfjFa7sIZwssiaYdS0cA%3D%3D&amp;trackingId=IAlrHxbZ1Kpz6NUhhEGjhw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/rci-pg-15229-1-senior-procurement-analyst-at-rangam-4386545763?position=7&amp;pageNum=0&amp;refId=Nrq7IF39VCC0tp9ZS6DloA%3D%3D&amp;trackingId=W51c8G5dk9Tg0EJ9ht6ylA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/rci-pg-15229-1-senior-procurement-analyst-at-rangam-4386545763?position=7&amp;pageNum=0&amp;refId=yTdWpKnNlfg3RgpU0%2FH4CA%3D%3D&amp;trackingId=u9IYBIrtiNbnSuA%2BRRppaA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3774,7 +3774,7 @@
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/retail-construction-materials-buyer-at-lush-fresh-handmade-cosmetics-north-america-4383399680?position=9&amp;pageNum=0&amp;refId=Nrq7IF39VCC0tp9ZS6DloA%3D%3D&amp;trackingId=alOpijuCSHY%2FzQ4DoWbpag%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/retail-construction-materials-buyer-at-lush-fresh-handmade-cosmetics-north-america-4383399680?position=9&amp;pageNum=0&amp;refId=yTdWpKnNlfg3RgpU0%2FH4CA%3D%3D&amp;trackingId=VZ42qCAZ8rspvqj2peOX7w%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/talent-sourcing-specialist-at-cherry-coatings-4386511602?position=15&amp;pageNum=0&amp;refId=Nrq7IF39VCC0tp9ZS6DloA%3D%3D&amp;trackingId=pULFdXKQreZu%2Br92Bu%2BQjQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/talent-sourcing-specialist-at-cherry-coatings-4386511602?position=15&amp;pageNum=0&amp;refId=yTdWpKnNlfg3RgpU0%2FH4CA%3D%3D&amp;trackingId=JfjpcYIuEq3ENrjMwYAN%2Fw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/associate-client-operations-open-to-remote-at-lensa-4386343692?position=23&amp;pageNum=0&amp;refId=Nrq7IF39VCC0tp9ZS6DloA%3D%3D&amp;trackingId=71Ffcbq5epzICAfph8iTvw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/associate-client-operations-open-to-remote-at-lensa-4386343692?position=23&amp;pageNum=0&amp;refId=yTdWpKnNlfg3RgpU0%2FH4CA%3D%3D&amp;trackingId=vRv85ethxQwQIPWPuCgnvQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/scheduling-specialist-remote-at-community-health-systems-4386516374?position=24&amp;pageNum=0&amp;refId=Nrq7IF39VCC0tp9ZS6DloA%3D%3D&amp;trackingId=Ka4EKdsgjpijqM3WdFcJ%2Bg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/scheduling-specialist-remote-at-community-health-systems-4386516374?position=24&amp;pageNum=0&amp;refId=yTdWpKnNlfg3RgpU0%2FH4CA%3D%3D&amp;trackingId=uSlsGQgW18FfIs5K030zRA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -3958,7 +3958,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/client-portfolio-manager-%E2%80%93-government-contract-consulting-at-capitol-50-consultants-inc-4386527581?position=4&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=%2FvWniSUbNYRqUbXtXB%2F2Bw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/client-portfolio-manager-%E2%80%93-government-contract-consulting-at-capitol-50-consultants-inc-4386527581?position=4&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=iOLRzylQ0SUcFBh2I%2F51oA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/quality-control-manager-at-lensa-4386359236?position=6&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=00nq1h%2FWqiMg4uq9X8%2BHoA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/quality-control-manager-at-lensa-4386359236?position=6&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=xJM5dHwSSc9Aa%2BjUtqtQfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/program-manager-%E2%80%93-contract-lifecycle-management-implementation-at-eliassen-group-4385612230?position=7&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=OcXjVSoXGVvdJ1AO3d3vbw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/program-manager-%E2%80%93-contract-lifecycle-management-implementation-at-eliassen-group-4385612230?position=7&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=LTu7baUE9QMSZDx6FeteLw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/project-manager-meter-data-management-cc-b-at-ntech-workforce-4382473398?position=8&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=lgHl3Tf2UeGTHTPwWQ24Tg%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/project-manager-meter-data-management-cc-b-at-ntech-workforce-4382473398?position=8&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=CsDKhaVdW71UQOWqyCT0uA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="J78" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/clinical-project-manager-assistant-homebased-at-actalent-4386513536?position=9&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=pU6YbbHboKdt1SE00Z0nvw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/clinical-project-manager-assistant-homebased-at-actalent-4386513536?position=9&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=wcGA1cFkOoevWqX04IGE8Q%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/medical-office-manager-remote-at-talent-bridge-4386300447?position=10&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=K5HNnbcnGc5BmY5F%2FfYngw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/medical-office-manager-remote-at-talent-bridge-4386300447?position=10&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=rUDnooDX3KPY0JQIS9rUxA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/recruiting-operations-specialist-at-dexian-4385611443?position=11&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=k3g7euHzsSorIbP94WnPAQ%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/recruiting-operations-specialist-at-dexian-4385611443?position=11&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=T%2BASYlq5F0PEqwcohtf8LQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/sr-project-manager-at-bma-doors-4384065667?position=12&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=IJL0TJGflNFbrrxBOugvuA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/sr-project-manager-at-bma-doors-4384065667?position=12&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=WPXh3hmf0d6srRLrUl%2FmZg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/100%25-remote-ai-first-project-manager-hands-on-llm-assistants-hipaa-jira-agile-pm-immediate-interviews-direct-client-at-accion-labs-4386337782?position=13&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=nYt1XUqtEpLOsia8q6fp3w%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/100%25-remote-ai-first-project-manager-hands-on-llm-assistants-hipaa-jira-agile-pm-immediate-interviews-direct-client-at-accion-labs-4386337782?position=13&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=odTdeYhp3OzaDBvhZQcQbw%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4372,7 +4372,7 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/communications-change-manager-at-infojini-inc-4386383596?position=14&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=OfqJNDZYs8fRNn3dLtFsqw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/communications-change-manager-at-infojini-inc-4386383596?position=14&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=%2Br1MzrzRVNNpLSfg7lE0Fg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-cmc-project-manager-at-aurion-biotech-4386528115?position=15&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=l1ONA2oBd%2BL7ipwD4Qd9dA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-cmc-project-manager-at-aurion-biotech-4386528115?position=15&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=wqbfoWXkjGCgQlUBRNp%2BNA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/head-of-ehs-mi-us-canada-at-lensa-4386365011?position=16&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=cIWqkS9nFacPNuxhwx7eKA%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/head-of-ehs-mi-us-canada-at-lensa-4386365011?position=16&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=wr1SAZy9NaI44XvP8m6Pqg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-construction-project-manager-data-center-at-epc-project-management-consulting-llc-4386332712?position=17&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=S3A8YmM%2F8acBtBGIHR7Bsw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-construction-project-manager-data-center-at-epc-project-management-consulting-llc-4386332712?position=17&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=Y0QoLYIkS8PHsvbSSliXkg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/microsoft-security-compliance-manager-it-audit-remote-at-dataedge-consulting-4384078501?position=19&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=ED7o0ipCEG%2FhqgwP47zFHw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/microsoft-security-compliance-manager-it-audit-remote-at-dataedge-consulting-4384078501?position=19&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=bdEDgAWlqBrJr96z9IScqg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4602,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-project-manager-at-it-resources-4386371253?position=20&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=2Brjtk4gPe2aO7IsRHOXHw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-project-manager-at-it-resources-4386371253?position=20&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=tqxFp0IXlKIJGEZFJhsKKg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/ln-concerts-sr-construction-project-manager-at-ladders-4384064185?position=21&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=GgZ%2B%2Bl9NB8OZ41mcamYFKw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/ln-concerts-sr-construction-project-manager-at-ladders-4384064185?position=21&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=oS9KYh%2BvoSiDdI4yt1%2Bhqg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/construction-project-manager-quick-service-restaurant-at-stansell-construction-4371935153?position=22&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=CQIa4t5W4%2BCOdB6ga0Vj6A%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/construction-project-manager-quick-service-restaurant-at-stansell-construction-4371935153?position=22&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=jYQvgh4uZTPxfHaVH1HEkA%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/senior-commercial-lines-account-manager-at-capstone-search-group-4386551294?position=23&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=eC4t2FxarO0aDSudGFd1mw%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/senior-commercial-lines-account-manager-at-capstone-search-group-4386551294?position=23&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=uoYmTsPffaUyXbGCFl9gFQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Raleigh, NC</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="E92" s="3" t="inlineStr"/>
@@ -4786,7 +4786,53 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/technical-project-manager-at-rithum-4386515260?position=24&amp;pageNum=0&amp;refId=g6B170jJAuU36UtkUsqYmg%3D%3D&amp;trackingId=WKYilc%2BEwtFqngGsimfB4A%3D%3D</t>
+          <t>https://www.linkedin.com/jobs/view/technical-project-manager-at-rithum-4386517342?position=24&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=XiVoqSiUiAfft1kwdhb5yg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Lead Supplier Performance Engineer</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Westinghouse Electric Company</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Hopkins, SC</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr"/>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>On-site</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Linkedin</t>
+        </is>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>contract manager remote</t>
+        </is>
+      </c>
+      <c r="J93" s="7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/lead-supplier-performance-engineer-at-westinghouse-electric-company-4331598645?position=25&amp;pageNum=0&amp;refId=SlA%2Fs%2B28TuNoj%2FcBOmnPfw%3D%3D&amp;trackingId=OV6bPV5BulFgt%2BM%2FqsSI%2FQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -4884,6 +4930,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J91" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4912,7 +4959,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>Generated: 2026-03-17 00:26</t>
+          <t>Generated: 2026-03-17 00:30</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4989,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7">
@@ -5003,7 +5050,7 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
